--- a/data/trans_bre/IP19C05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Edad-trans_bre.xlsx
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,53</t>
+          <t>-2,64; 1,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,15</t>
+          <t>-2,63; 1,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 0,66</t>
+          <t>-3,89; 1,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 5,67</t>
+          <t>-0,87; 5,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,52</t>
+          <t>-0,9; 3,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-67,04; 1198,36</t>
+          <t>-58,36; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,79</t>
+          <t>-0,78; 2,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,46</t>
+          <t>-2,62; 3,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 4,8</t>
+          <t>-3,19; 4,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,61; 332,94</t>
+          <t>-76,11; 359,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,26; 353,87</t>
+          <t>-61,96; 247,41</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,13</t>
+          <t>-1,22; 1,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,9</t>
+          <t>-0,74; 2,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,59</t>
+          <t>-0,91; 2,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-81,22; 309,13</t>
+          <t>-79,37; 404,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 396,35</t>
+          <t>-37,13; 299,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 297,13</t>
+          <t>-38,44; 320,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Edad-trans_bre.xlsx
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,55</t>
+          <t>-3,41; 1,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,15</t>
+          <t>-2,53; 1,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,12</t>
+          <t>-4,37; 0,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 5,77</t>
+          <t>-0,78; 5,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,36</t>
+          <t>-0,92; 3,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,36; —</t>
+          <t>-73,82; 1068,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,83</t>
+          <t>-0,95; 2,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 3,53</t>
+          <t>-2,53; 3,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,43</t>
+          <t>-3,22; 4,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,11; 359,49</t>
+          <t>-70,25; 404,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,96; 247,41</t>
+          <t>-61,59; 319,14</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,27</t>
+          <t>-1,18; 1,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,74</t>
+          <t>-0,79; 2,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,7</t>
+          <t>-0,93; 2,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-79,37; 404,08</t>
+          <t>-81,02; 379,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 299,11</t>
+          <t>-39,77; 258,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 320,9</t>
+          <t>-41,91; 242,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Edad-trans_bre.xlsx
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,54</t>
+          <t>-3,09; 1,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,15</t>
+          <t>-3,18; 1,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,65</t>
+          <t>-4,46; 0,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 5,68</t>
+          <t>-1,05; 5,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,38</t>
+          <t>-0,94; 3,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,82; 1068,83</t>
+          <t>-67,04; 1198,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,51</t>
+          <t>-1,1; 2,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,95</t>
+          <t>-2,82; 3,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,81</t>
+          <t>-3,58; 4,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,25; 404,01</t>
+          <t>-76,61; 332,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,59; 319,14</t>
+          <t>-64,26; 353,87</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,22</t>
+          <t>-1,24; 1,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,75</t>
+          <t>-0,74; 2,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,58</t>
+          <t>-0,79; 2,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-81,02; 379,39</t>
+          <t>-81,22; 309,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 258,1</t>
+          <t>-35,86; 396,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 242,58</t>
+          <t>-38,01; 297,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C05-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,115 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-10,67%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-27,08%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,09; 1,53</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,18; 1,15</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+      <c r="C7" s="5" t="n">
+        <v>-0.09088212101903501</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.211735731374949</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.1066844686063903</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2708482643511093</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,05</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,97</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-56,16%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>129,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>108,94%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.092869094744501</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.17997107233123</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,46; 0,66</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,05; 5,67</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,94; 3,52</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-67,04; 1198,36</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.530029722477574</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.146568937894356</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +719,231 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73,73%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,41%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.8290685018824899</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.048855139804537</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.969996541556988</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.5616118469098239</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1.298572449502403</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.089436262540872</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,1; 2,79</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,82; 3,46</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,58; 4,8</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-76,61; 332,94</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-64,26; 353,87</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.461900507536001</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.051869776874004</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.9355868425851855</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="n">
+        <v>-0.67040959438979</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.656287184176387</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.670070843730191</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.52102107531015</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="n">
+        <v>11.98357472439538</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5458664282912674</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4933766229687574</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.7992072237853171</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.7373465370714017</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.2040276047808427</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2241334564031634</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.098242907993085</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.815958244461435</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.577835071937577</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-0.7661288050739524</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6426149544441745</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.788602818604926</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.45618582148942</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.799970392404776</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>3.329370804858145</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3.538698273518252</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,16%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>54,41%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>50,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,24; 1,13</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,74; 2,9</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,79; 2,59</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-81,22; 309,13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-35,86; 396,35</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-38,01; 297,13</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.01129055055764383</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9243879343079033</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8388304965545604</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.01156439558567262</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.5441273032485812</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.5017371236590873</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.236873151634271</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.7366684071880731</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.7905734161701663</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.8122246853555277</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3585518719476887</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3800751984856841</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.125210289242748</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.904313393394856</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.589864854486734</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>3.091292136617253</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>3.963457609350142</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2.971283089795334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +952,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
